--- a/artfynd/A 2549-2026 artfynd.xlsx
+++ b/artfynd/A 2549-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132246431</v>
       </c>
       <c r="B2" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132246438</v>
       </c>
       <c r="B3" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2549-2026 artfynd.xlsx
+++ b/artfynd/A 2549-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132246431</v>
       </c>
       <c r="B2" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132246438</v>
       </c>
       <c r="B3" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2549-2026 artfynd.xlsx
+++ b/artfynd/A 2549-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132246431</v>
       </c>
       <c r="B2" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132246438</v>
       </c>
       <c r="B3" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2549-2026 artfynd.xlsx
+++ b/artfynd/A 2549-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132246431</v>
       </c>
       <c r="B2" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132246438</v>
       </c>
       <c r="B3" t="n">
-        <v>91928</v>
+        <v>91929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2549-2026 artfynd.xlsx
+++ b/artfynd/A 2549-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132246431</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132246438</v>
       </c>
       <c r="B3" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2549-2026 artfynd.xlsx
+++ b/artfynd/A 2549-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132246431</v>
       </c>
       <c r="B2" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132246438</v>
       </c>
       <c r="B3" t="n">
-        <v>91930</v>
+        <v>91932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2549-2026 artfynd.xlsx
+++ b/artfynd/A 2549-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132246431</v>
       </c>
       <c r="B2" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132246438</v>
       </c>
       <c r="B3" t="n">
-        <v>91932</v>
+        <v>91933</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
